--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Rydevik, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elin Rydevik</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elin Rydevik</t>
+          <t>Elin Rydevik, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53611-2024 artfynd.xlsx
+++ b/artfynd/A 53611-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136552146</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136552169</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136551879</v>
       </c>
       <c r="B4" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
